--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -282,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -296,11 +296,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -431,6 +459,8 @@
     <xf numFmtId="0" fontId="34" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +539,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -645,7 +674,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -770,7 +798,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -833,7 +860,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -961,7 +987,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1089,7 +1114,6 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1226,7 +1250,6 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1356,7 +1379,6 @@
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3447,21 +3469,21 @@
           <t>Phase 1: Discovery &amp; Assessment [COMPLETED]</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
+      <c r="B6" s="96" t="n"/>
+      <c r="C6" s="96" t="n"/>
+      <c r="D6" s="96" t="n"/>
+      <c r="E6" s="96" t="n"/>
+      <c r="F6" s="96" t="n"/>
+      <c r="G6" s="96" t="n"/>
+      <c r="H6" s="96" t="n"/>
+      <c r="I6" s="96" t="n"/>
+      <c r="J6" s="96" t="n"/>
+      <c r="K6" s="96" t="n"/>
+      <c r="L6" s="96" t="n"/>
+      <c r="M6" s="96" t="n"/>
+      <c r="N6" s="96" t="n"/>
+      <c r="O6" s="96" t="n"/>
+      <c r="P6" s="97" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -4099,21 +4121,21 @@
           <t>Phase 2: Planning &amp; Design</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96" t="n"/>
+      <c r="F17" s="96" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="96" t="n"/>
+      <c r="J17" s="96" t="n"/>
+      <c r="K17" s="96" t="n"/>
+      <c r="L17" s="96" t="n"/>
+      <c r="M17" s="96" t="n"/>
+      <c r="N17" s="96" t="n"/>
+      <c r="O17" s="96" t="n"/>
+      <c r="P17" s="97" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -4709,21 +4731,21 @@
           <t>Phase 3: Build &amp; Prepare</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="96" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="96" t="n"/>
+      <c r="I27" s="96" t="n"/>
+      <c r="J27" s="96" t="n"/>
+      <c r="K27" s="96" t="n"/>
+      <c r="L27" s="96" t="n"/>
+      <c r="M27" s="96" t="n"/>
+      <c r="N27" s="96" t="n"/>
+      <c r="O27" s="96" t="n"/>
+      <c r="P27" s="97" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -5451,21 +5473,21 @@
           <t>Phase 4: Migration Execution</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
+      <c r="B39" s="96" t="n"/>
+      <c r="C39" s="96" t="n"/>
+      <c r="D39" s="96" t="n"/>
+      <c r="E39" s="96" t="n"/>
+      <c r="F39" s="96" t="n"/>
+      <c r="G39" s="96" t="n"/>
+      <c r="H39" s="96" t="n"/>
+      <c r="I39" s="96" t="n"/>
+      <c r="J39" s="96" t="n"/>
+      <c r="K39" s="96" t="n"/>
+      <c r="L39" s="96" t="n"/>
+      <c r="M39" s="96" t="n"/>
+      <c r="N39" s="96" t="n"/>
+      <c r="O39" s="96" t="n"/>
+      <c r="P39" s="97" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -6199,21 +6221,21 @@
           <t>Phase 4a: Testing (IQE-Led)</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="n"/>
-      <c r="N51" s="10" t="n"/>
-      <c r="O51" s="10" t="n"/>
-      <c r="P51" s="10" t="n"/>
+      <c r="B51" s="96" t="n"/>
+      <c r="C51" s="96" t="n"/>
+      <c r="D51" s="96" t="n"/>
+      <c r="E51" s="96" t="n"/>
+      <c r="F51" s="96" t="n"/>
+      <c r="G51" s="96" t="n"/>
+      <c r="H51" s="96" t="n"/>
+      <c r="I51" s="96" t="n"/>
+      <c r="J51" s="96" t="n"/>
+      <c r="K51" s="96" t="n"/>
+      <c r="L51" s="96" t="n"/>
+      <c r="M51" s="96" t="n"/>
+      <c r="N51" s="96" t="n"/>
+      <c r="O51" s="96" t="n"/>
+      <c r="P51" s="97" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -6617,21 +6639,21 @@
           <t>Phase 5: Post-Migration Optimize</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
+      <c r="B58" s="96" t="n"/>
+      <c r="C58" s="96" t="n"/>
+      <c r="D58" s="96" t="n"/>
+      <c r="E58" s="96" t="n"/>
+      <c r="F58" s="96" t="n"/>
+      <c r="G58" s="96" t="n"/>
+      <c r="H58" s="96" t="n"/>
+      <c r="I58" s="96" t="n"/>
+      <c r="J58" s="96" t="n"/>
+      <c r="K58" s="96" t="n"/>
+      <c r="L58" s="96" t="n"/>
+      <c r="M58" s="96" t="n"/>
+      <c r="N58" s="96" t="n"/>
+      <c r="O58" s="96" t="n"/>
+      <c r="P58" s="97" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -8327,6 +8349,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8462,7 +8486,7 @@
         <v>68</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>14</v>
@@ -8509,7 +8533,7 @@
         <v>108</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>18</v>
@@ -8556,7 +8580,7 @@
         <v>83</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>14</v>
@@ -8603,7 +8627,7 @@
         <v>43</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>15</v>
@@ -8650,7 +8674,7 @@
         <v>30</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>8</v>
@@ -8697,7 +8721,7 @@
         <v>53</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>9</v>
@@ -8744,7 +8768,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>6</v>
@@ -8791,7 +8815,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>5</v>
@@ -8838,7 +8862,7 @@
         <v>68</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>4</v>
@@ -8885,7 +8909,7 @@
         <v>48</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>8</v>
@@ -8959,6 +8983,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -9413,6 +9439,7 @@
   <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>

--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Revenue View" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool vs Industry Benchmark" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost by Cloud" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="+0%;-0%"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -207,6 +208,14 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -328,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -461,6 +470,10 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="37" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8349,8 +8362,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8983,8 +8994,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12410,4 +12419,498 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PG&amp;E Migration Cost by Cloud Platform — Concierto Migrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>415 Apps | 4,273 Servers | Discovery COMPLETED | PG&amp;E provides LZ/Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Section A: Migration Duration by Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Servers</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Traditional
+Days</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>AI Factor</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>AI Days</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Days Saved</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Savings %</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Months
+Saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="98" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="E6" s="79" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F6" s="5">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>D6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="79">
+        <f>IF(D6&gt;0,(D6-F6)/D6,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="5">
+        <f>ROUND(G6/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="98" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>852</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>538</v>
+      </c>
+      <c r="E7" s="79" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F7" s="5">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>D7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="79">
+        <f>IF(D7&gt;0,(D7-F7)/D7,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>ROUND(G7/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="98" t="inlineStr">
+        <is>
+          <t>Azure Local / HyperV</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2702</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>586</v>
+      </c>
+      <c r="E8" s="79" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F8" s="5">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>D8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="79">
+        <f>IF(D8&gt;0,(D8-F8)/D8,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>ROUND(G8/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <f>SUM(B6:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>SUM(G6:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="87">
+        <f>IF(D9&gt;0,(D9-F9)/D9,0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>ROUND(G9/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Section B: Migration Cost by Cloud (2-Year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>AI Days</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Avg FTEs</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Blended
+Rate ($)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Y1 Labor ($)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Y2 Labor
+(13% SS)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Platform
+License ($)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Tooling &amp;
+Other ($)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2-Year Total ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="98" t="inlineStr">
+        <is>
+          <t>AWS (107 apps)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E14" s="22">
+        <f>B14*C14*D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>E14*0.13</f>
+        <v/>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I14" s="22">
+        <f>E14+F14+G14+H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="98" t="inlineStr">
+        <is>
+          <t>Azure (145 apps)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E15" s="22">
+        <f>B15*C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>E15*0.13</f>
+        <v/>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I15" s="22">
+        <f>E15+F15+G15+H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="98" t="inlineStr">
+        <is>
+          <t>Azure Local/HV (130 apps)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E16" s="22">
+        <f>B16*C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>E16*0.13</f>
+        <v/>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I16" s="22">
+        <f>E16+F16+G16+H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Contingency (12%)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="22">
+        <f>SUM(I14:I16)*0.12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (2-Year)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="23">
+        <f>SUM(E14:E16)</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>SUM(F14:F16)</f>
+        <v/>
+      </c>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="23">
+        <f>SUM(I14:I16)+I17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>Traditional 2-Year (No AI)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="99" t="n">
+        <v>12349312.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="77" t="inlineStr">
+        <is>
+          <t>NET SAVINGS</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="100">
+        <f>I20-I18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Tool: Concierto Migrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="101" t="inlineStr">
+        <is>
+          <t>Full multi-cloud coverage. Strong rehost (CloudMach) + modernize</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -8362,6 +8362,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8494,13 +8496,13 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="21" t="n">
         <v>1100</v>
@@ -8541,13 +8543,13 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F36" s="21" t="n">
         <v>1050</v>
@@ -8588,13 +8590,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F37" s="21" t="n">
         <v>1050</v>
@@ -8635,13 +8637,13 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D38" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>17</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>15</v>
       </c>
       <c r="F38" s="21" t="n">
         <v>1000</v>
@@ -8682,13 +8684,13 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="21" t="n">
         <v>1100</v>
@@ -8729,13 +8731,13 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F40" s="21" t="n">
         <v>1000</v>
@@ -8776,13 +8778,13 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" s="21" t="n">
         <v>1050</v>
@@ -8823,13 +8825,13 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F42" s="21" t="n">
         <v>1100</v>
@@ -8870,13 +8872,13 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="21" t="n">
         <v>1100</v>
@@ -8917,13 +8919,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44" s="21" t="n">
         <v>1050</v>
@@ -8994,6 +8996,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>

--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -8496,10 +8496,10 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8687,7 +8687,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8781,7 +8781,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>
@@ -12725,7 +12725,7 @@
         <v>208</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12759,7 +12759,7 @@
         <v>210</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>1050</v>
@@ -12793,7 +12793,7 @@
         <v>229</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>1050</v>
@@ -12873,7 +12873,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="99" t="n">
-        <v>12349312.5</v>
+        <v>10840125</v>
       </c>
     </row>
     <row r="21">

--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -8362,8 +8362,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8996,8 +8994,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12725,7 +12721,7 @@
         <v>208</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12739,10 +12735,10 @@
         <v/>
       </c>
       <c r="G14" s="22" t="n">
-        <v>40000</v>
+        <v>26667</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I14" s="22">
         <f>E14+F14+G14+H14</f>
@@ -12759,7 +12755,7 @@
         <v>210</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>1050</v>
@@ -12773,10 +12769,10 @@
         <v/>
       </c>
       <c r="G15" s="22" t="n">
-        <v>40000</v>
+        <v>26667</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I15" s="22">
         <f>E15+F15+G15+H15</f>
@@ -12793,7 +12789,7 @@
         <v>229</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>1050</v>
@@ -12807,10 +12803,10 @@
         <v/>
       </c>
       <c r="G16" s="22" t="n">
-        <v>40000</v>
+        <v>26667</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I16" s="22">
         <f>E16+F16+G16+H16</f>
@@ -12873,7 +12869,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="99" t="n">
-        <v>10840125</v>
+        <v>10174500</v>
       </c>
     </row>
     <row r="21">

--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -8362,6 +8362,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8494,10 +8496,10 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8541,10 +8543,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8588,10 +8590,10 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8635,10 +8637,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8685,7 +8687,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8729,10 +8731,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8779,7 +8781,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8823,10 +8825,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8870,10 +8872,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8917,10 +8919,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>
@@ -8994,6 +8996,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>

--- a/sample_data/Concierto_Migrate.xlsx
+++ b/sample_data/Concierto_Migrate.xlsx
@@ -8362,8 +8362,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8996,8 +8994,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12725,7 +12721,7 @@
         <v>208</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12873,7 +12869,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="99" t="n">
-        <v>10174500</v>
+        <v>10894125</v>
       </c>
     </row>
     <row r="21">
